--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484805_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484805_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9908</v>
+        <v>7.8458</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7877</v>
+        <v>6.4311</v>
       </c>
       <c r="F2" t="n">
-        <v>1.203</v>
+        <v>1.4147</v>
       </c>
       <c r="G2" t="n">
         <v>6.1974</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6972</v>
+        <v>0.1579</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9871</v>
+        <v>-0.3437</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2899</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.9244</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2824</v>
+        <v>3.4974</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3888</v>
+        <v>1.6038</v>
       </c>
       <c r="F3" t="n">
         <v>1.8937</v>
@@ -688,10 +688,10 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1052</v>
+        <v>0.3202</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0152</v>
+        <v>0.2302</v>
       </c>
       <c r="U3" t="n">
         <v>0.09</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GOMEZ AGUADO</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6106</v>
+        <v>1.6671</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8332</v>
+        <v>1.0062</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2226</v>
+        <v>0.6609</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4807</v>
+        <v>2.4465</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4807</v>
+        <v>1.3743</v>
       </c>
       <c r="J4" t="n">
-        <v>1.892</v>
+        <v>3.4221</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.4634</v>
       </c>
       <c r="L4" t="n">
-        <v>1.892</v>
+        <v>1.9587</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4113</v>
+        <v>-0.9756</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.3913</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4113</v>
+        <v>-0.5843</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0588</v>
+        <v>0.4848</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0588</v>
+        <v>0.1127</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.3721</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2642</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>M. GOMEZ AGUADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5335</v>
+        <v>1.6106</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0392</v>
+        <v>1.8332</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5727</v>
+        <v>-0.2226</v>
       </c>
       <c r="G5" t="n">
-        <v>0.789</v>
+        <v>1.4807</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1958</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4068</v>
+        <v>1.4807</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8191</v>
+        <v>1.892</v>
       </c>
       <c r="K5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.329</v>
+        <v>1.892</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.03</v>
+        <v>-0.4113</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2942</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7358</v>
+        <v>-0.4113</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8305</v>
+        <v>0.1887</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3861</v>
+        <v>-0.0588</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3121</v>
+        <v>-0.0588</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0741</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9339</v>
+        <v>1.0761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9339</v>
+        <v>-1.3114</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.3875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9339</v>
+        <v>0.789</v>
       </c>
       <c r="H6" t="n">
-        <v>0.317</v>
+        <v>1.1958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.617</v>
+        <v>-0.4068</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9339</v>
+        <v>1.8191</v>
       </c>
       <c r="K6" t="n">
-        <v>0.317</v>
+        <v>1.49</v>
       </c>
       <c r="L6" t="n">
-        <v>0.617</v>
+        <v>0.329</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.2942</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.7358</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.9288</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4684</v>
+        <v>0.9339</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.013</v>
+        <v>0.9339</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4813</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4789</v>
+        <v>0.9339</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4305</v>
+        <v>0.317</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9094</v>
+        <v>0.617</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7866</v>
+        <v>0.9339</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5057</v>
+        <v>0.317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2809</v>
+        <v>0.617</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2655</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0752</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1902</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3966</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0794</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5726</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3875</v>
+        <v>0.6582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.5056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.317</v>
+        <v>1.1639</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4465</v>
+        <v>-0.4789</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0722</v>
+        <v>0.4305</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3743</v>
+        <v>-0.9094</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4221</v>
+        <v>1.7866</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4634</v>
+        <v>1.5057</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9587</v>
+        <v>0.2809</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9756</v>
+        <v>-2.2655</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3913</v>
+        <v>-1.0752</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5843</v>
+        <v>-1.1902</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>3.3966</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7948</v>
+        <v>0.2693</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.823</v>
+        <v>-0.0653</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0282</v>
+        <v>0.3346</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2642</v>
+        <v>0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.6036</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1378</v>
+        <v>0.2179</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6213</v>
+        <v>-1.5037</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4835</v>
+        <v>1.7216</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1956</v>
@@ -1156,13 +1156,13 @@
         <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9611</v>
+        <v>-0.6055</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2323</v>
+        <v>-0.1147</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7289</v>
+        <v>-0.4908</v>
       </c>
       <c r="V9" t="n">
         <v>0.6415999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1643</v>
+        <v>0.0751</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.92</v>
+        <v>-0.6277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7557</v>
+        <v>0.7028</v>
       </c>
       <c r="G10" t="n">
         <v>0.6504</v>
@@ -1234,13 +1234,13 @@
         <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0599</v>
+        <v>0.1794</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0588</v>
+        <v>0.2335</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7368</v>
+        <v>-1.6124</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9983</v>
+        <v>-1.5829</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2615</v>
+        <v>-0.0295</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1473</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7125</v>
+        <v>-0.1631</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6525</v>
+        <v>0.0679</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06</v>
+        <v>-0.231</v>
       </c>
       <c r="V11" t="n">
         <v>1.2642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8921</v>
+        <v>-1.6548</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6079</v>
+        <v>-0.3665</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4999</v>
+        <v>-1.2883</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5875</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4503</v>
+        <v>-0.3124</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3608</v>
+        <v>0.3865</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9105</v>
+        <v>-0.6989</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3464</v>
+        <v>-2.7974</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7458</v>
+        <v>-2.0381</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6006</v>
+        <v>-0.7594</v>
       </c>
       <c r="G13" t="n">
         <v>3.7881</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6584</v>
+        <v>0.2074</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2504</v>
+        <v>-0.0419</v>
       </c>
       <c r="U13" t="n">
-        <v>0.408</v>
+        <v>0.2493</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8868</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.9297</v>
+        <v>11.5175</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2844</v>
+        <v>3.872300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>7.645300000000001</v>
+        <v>7.6453</v>
       </c>
       <c r="G14" t="n">
         <v>13.9026</v>
@@ -1528,7 +1528,7 @@
         <v>17.0992</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.2439</v>
+        <v>-8.243899999999998</v>
       </c>
       <c r="N14" t="n">
         <v>-5.5405</v>
@@ -1546,13 +1546,13 @@
         <v>19.8135</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8200999999999998</v>
+        <v>1.408</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1416000000000001</v>
+        <v>0.4463</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9616000000000002</v>
+        <v>0.9615999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-0.01899999999999991</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6923</v>
+        <v>6.9734</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8959</v>
+        <v>4.9676</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7965</v>
+        <v>2.0057</v>
       </c>
       <c r="G15" t="n">
         <v>4.5257</v>
@@ -1624,13 +1624,13 @@
         <v>3.5853</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1163</v>
+        <v>0.1648</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1634</v>
+        <v>-0.0916</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0471</v>
+        <v>0.2564</v>
       </c>
       <c r="V15" t="n">
         <v>0.5846</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6631</v>
+        <v>1.6768</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8542</v>
+        <v>0.6849</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1702</v>
@@ -1702,13 +1702,13 @@
         <v>3.2079</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2292</v>
+        <v>0.2428</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5524</v>
+        <v>0.3832</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3232</v>
+        <v>-0.1404</v>
       </c>
       <c r="V16" t="n">
         <v>0.3398</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2299</v>
+        <v>0.317</v>
       </c>
       <c r="E18" t="n">
-        <v>1.93</v>
+        <v>0.317</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7000999999999999</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.55</v>
+        <v>0.317</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.245</v>
+        <v>0.317</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3049</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5695</v>
+        <v>0.317</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1214</v>
+        <v>0.317</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4481</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1194</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3664</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.753</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.7175</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0192</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3086</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3614</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9471000000000001</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,55 +1891,55 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.317</v>
+        <v>0.2471</v>
       </c>
       <c r="E19" t="n">
-        <v>0.317</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1548</v>
       </c>
       <c r="G19" t="n">
-        <v>0.317</v>
+        <v>-0.3902</v>
       </c>
       <c r="H19" t="n">
-        <v>0.317</v>
+        <v>0.0211</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="J19" t="n">
-        <v>0.317</v>
+        <v>0.0211</v>
       </c>
       <c r="K19" t="n">
-        <v>0.317</v>
+        <v>0.0211</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.0711</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.0711</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2471</v>
+        <v>0.1487</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.248</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1548</v>
+        <v>-1.0993</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3902</v>
+        <v>-0.55</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0211</v>
+        <v>-0.245</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4113</v>
+        <v>-0.3049</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0211</v>
+        <v>2.5695</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0211</v>
+        <v>1.1214</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.4481</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4113</v>
+        <v>-3.1194</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.3664</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4113</v>
+        <v>-1.753</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.7175</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5661</v>
+        <v>3.0192</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0711</v>
+        <v>0.2273</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0711</v>
+        <v>-0.3206</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5949</v>
+        <v>-1.5262</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0994</v>
+        <v>0.1968</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6943</v>
+        <v>-1.7231</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8711</v>
@@ -2092,13 +2092,13 @@
         <v>2.8305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2005</v>
+        <v>0.2691</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3375</v>
+        <v>-0.2401</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5379</v>
+        <v>0.5091</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8112</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0861</v>
+        <v>-2.0597</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3196</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.7401</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1558</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2886</v>
+        <v>-0.2622</v>
       </c>
       <c r="T22" t="n">
         <v>0.0152</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3039</v>
+        <v>-0.2774</v>
       </c>
       <c r="V22" t="n">
         <v>0.3018</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2683</v>
+        <v>-2.6483</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8476</v>
+        <v>-3.0425</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5793</v>
+        <v>0.3941</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4577</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7366</v>
+        <v>0.3565</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4391</v>
+        <v>0.2442</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2975</v>
+        <v>0.1123</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.61</v>
+        <v>-4.6726</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.524</v>
+        <v>-2.7188</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0861</v>
+        <v>-1.9538</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9463</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2863</v>
+        <v>-0.3489</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1147</v>
+        <v>-0.3095</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6226</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8188</v>
+        <v>-4.8746</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8963</v>
+        <v>-5.9205</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9225</v>
+        <v>1.0458</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.4453</v>
+        <v>-7.3094</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1504</v>
+        <v>-1.9299</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2949</v>
+        <v>-5.3795</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.375</v>
+        <v>-4.0611</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1581</v>
+        <v>-1.6685</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2169</v>
+        <v>-2.3926</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.0704</v>
+        <v>-3.2483</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9923</v>
+        <v>-0.2614</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.0781</v>
+        <v>-2.9869</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.887</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6983</v>
+        <v>3.774</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.883</v>
+        <v>-0.4146</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6343</v>
+        <v>-0.2742</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2486</v>
+        <v>-0.1404</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3018</v>
+        <v>0.9624</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3018</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.2518</v>
+        <v>-5.4123</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.7974</v>
+        <v>-3.7014</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5456</v>
+        <v>-1.7109</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.3094</v>
+        <v>-4.4453</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9299</v>
+        <v>-1.1504</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.3795</v>
+        <v>-3.2949</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.0611</v>
+        <v>-1.375</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6685</v>
+        <v>-0.1581</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.3926</v>
+        <v>-1.2169</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.2483</v>
+        <v>-3.0704</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2614</v>
+        <v>-0.9923</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.9869</v>
+        <v>-2.0781</v>
       </c>
       <c r="P26" t="n">
-        <v>1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.887</v>
       </c>
       <c r="R26" t="n">
-        <v>3.774</v>
+        <v>1.6983</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7918</v>
+        <v>-0.4765</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1511</v>
+        <v>-0.4395</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6407</v>
+        <v>-0.037</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9624</v>
+        <v>-0.3018</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6606</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="27">
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.9296</v>
+        <v>-10.2798</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.6452</v>
+        <v>-7.645300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.2844</v>
+        <v>-2.635</v>
       </c>
       <c r="G27" t="n">
         <v>-13.9024</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4929999999999994</v>
+        <v>0.4929999999999997</v>
       </c>
       <c r="I27" t="n">
         <v>-14.3956</v>
       </c>
       <c r="J27" t="n">
-        <v>8.244</v>
+        <v>8.244000000000002</v>
       </c>
       <c r="K27" t="n">
         <v>5.540699999999999</v>
@@ -2560,16 +2560,16 @@
         <v>23.5875</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8199999999999998</v>
+        <v>-0.1706000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>-0.9618000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1416000000000002</v>
+        <v>0.7912</v>
       </c>
       <c r="V27" t="n">
-        <v>0.01900000000000002</v>
+        <v>0.01900000000000007</v>
       </c>
       <c r="W27" t="n">
         <v>4.8858</v>
